--- a/data/trans_camb/PCS12_SP_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R2-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 8,06</t>
+          <t>-2,79; 7,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 5,99</t>
+          <t>-4,46; 5,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 14,32</t>
+          <t>2,65; 14,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 0,93</t>
+          <t>-9,63; 1,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,43; -0,88</t>
+          <t>-10,63; -0,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,03</t>
+          <t>-7,61; 2,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 3,34</t>
+          <t>-4,49; 2,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 1,05</t>
+          <t>-6,46; 1,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 6,5</t>
+          <t>-1,11; 6,64</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 20,21</t>
+          <t>-6,15; 19,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 15,58</t>
+          <t>-9,78; 14,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 35,26</t>
+          <t>5,54; 34,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 1,64</t>
+          <t>-16,06; 2,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,2; -1,71</t>
+          <t>-17,67; -0,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 3,72</t>
+          <t>-12,71; 4,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 7,02</t>
+          <t>-8,7; 5,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 2,24</t>
+          <t>-12,4; 2,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 13,62</t>
+          <t>-2,26; 13,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 9,0</t>
+          <t>-0,24; 8,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 1,25</t>
+          <t>-7,06; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 33,26</t>
+          <t>-3,61; 33,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,18; -0,35</t>
+          <t>-9,7; -0,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,86; -8,97</t>
+          <t>-17,63; -8,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,15; -5,64</t>
+          <t>-14,14; -5,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,62</t>
+          <t>-3,48; 3,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,21; -4,75</t>
+          <t>-11,22; -4,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 16,57</t>
+          <t>-7,45; 17,36</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 24,0</t>
+          <t>-0,54; 24,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 3,63</t>
+          <t>-16,67; 5,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 88,52</t>
+          <t>-9,11; 86,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -0,63</t>
+          <t>-15,57; -0,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,59; -15,47</t>
+          <t>-28,39; -15,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -9,81</t>
+          <t>-22,52; -9,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 5,33</t>
+          <t>-6,82; 6,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,69; -9,77</t>
+          <t>-21,88; -10,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 34,43</t>
+          <t>-14,6; 35,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,12; -0,33</t>
+          <t>-11,61; -1,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,42; -0,86</t>
+          <t>-11,86; -1,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 3,84</t>
+          <t>-7,61; 3,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 0,95</t>
+          <t>-9,26; 1,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,03; -2,64</t>
+          <t>-12,98; -2,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 24,06</t>
+          <t>-8,97; 24,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,13; -0,95</t>
+          <t>-9,25; -1,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,62; -3,45</t>
+          <t>-10,97; -3,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 19,12</t>
+          <t>-6,13; 19,08</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,62; -0,7</t>
+          <t>-23,59; -2,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,16; -2,23</t>
+          <t>-23,84; -2,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 8,53</t>
+          <t>-15,5; 8,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 1,83</t>
+          <t>-15,77; 1,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,01; -4,96</t>
+          <t>-21,92; -4,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 43,16</t>
+          <t>-15,5; 42,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -1,95</t>
+          <t>-17,09; -2,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,94; -7,0</t>
+          <t>-20,48; -6,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 38,2</t>
+          <t>-11,58; 37,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 7,26</t>
+          <t>-1,57; 7,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,07; -1,3</t>
+          <t>-10,41; -1,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 14,64</t>
+          <t>5,31; 14,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,54</t>
+          <t>-3,26; 5,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -3,99</t>
+          <t>-12,67; -4,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 4,53</t>
+          <t>-11,0; 4,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 5,16</t>
+          <t>-1,48; 5,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,0; -3,8</t>
+          <t>-10,05; -4,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 8,16</t>
+          <t>-2,57; 7,87</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 17,96</t>
+          <t>-3,6; 19,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,66; -3,26</t>
+          <t>-23,19; -3,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,43; 36,18</t>
+          <t>12,0; 37,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 10,82</t>
+          <t>-5,72; 10,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,8; -7,57</t>
+          <t>-22,69; -7,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 8,55</t>
+          <t>-20,17; 8,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 11,04</t>
+          <t>-2,86; 11,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,05; -8,07</t>
+          <t>-20,23; -8,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 17,41</t>
+          <t>-4,96; 16,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,77</t>
+          <t>-0,97; 3,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,19; -1,13</t>
+          <t>-6,05; -1,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,64; 19,39</t>
+          <t>2,56; 17,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,3</t>
+          <t>-5,05; -0,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,7; -6,83</t>
+          <t>-11,47; -6,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 6,39</t>
+          <t>-6,17; 5,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,06</t>
+          <t>-2,46; 0,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,16; -4,81</t>
+          <t>-8,14; -4,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 8,91</t>
+          <t>-0,96; 9,1</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 9,16</t>
+          <t>-2,2; 9,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -2,73</t>
+          <t>-13,79; -2,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6,17; 46,13</t>
+          <t>5,88; 41,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,0; -0,55</t>
+          <t>-8,72; -0,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,12; -12,3</t>
+          <t>-19,76; -11,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 11,3</t>
+          <t>-10,94; 10,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,17</t>
+          <t>-4,85; 1,93</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -9,77</t>
+          <t>-16,08; -9,73</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 17,86</t>
+          <t>-1,89; 18,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/PCS12_SP_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R2-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,14</t>
+          <t>7,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-3,77</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 7,61</t>
+          <t>-2,86; 7,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 5,82</t>
+          <t>-4,95; 5,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 14,3</t>
+          <t>2,41; 13,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 1,25</t>
+          <t>-9,51; 0,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -0,2</t>
+          <t>-11,54; -0,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 2,38</t>
+          <t>-8,75; 0,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 2,89</t>
+          <t>-4,15; 2,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 1,35</t>
+          <t>-6,44; 0,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 6,64</t>
+          <t>-1,9; 5,48</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-5,09%</t>
+          <t>-6,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 19,04</t>
+          <t>-6,38; 18,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 14,58</t>
+          <t>-10,84; 13,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 34,9</t>
+          <t>5,09; 32,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 2,38</t>
+          <t>-15,8; 1,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,67; -0,35</t>
+          <t>-19,21; -1,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 4,34</t>
+          <t>-14,49; 1,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 5,99</t>
+          <t>-8,14; 6,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 2,85</t>
+          <t>-12,52; 2,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 13,74</t>
+          <t>-3,65; 11,37</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>-2,76</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,89</t>
+          <t>-10,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>-6,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 8,95</t>
+          <t>0,13; 9,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 1,9</t>
+          <t>-7,02; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 33,75</t>
+          <t>-7,07; 1,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,7; -0,28</t>
+          <t>-9,82; -0,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,63; -8,82</t>
+          <t>-18,17; -9,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -5,7</t>
+          <t>-14,52; -5,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,02</t>
+          <t>-3,89; 3,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,22; -4,77</t>
+          <t>-11,37; -5,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 17,36</t>
+          <t>-9,91; -3,53</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>-6,96%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,41%</t>
+          <t>-17,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>-13,04%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 24,42</t>
+          <t>0,25; 25,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 5,19</t>
+          <t>-16,74; 5,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 86,55</t>
+          <t>-17,23; 4,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,57; -0,59</t>
+          <t>-15,7; -1,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,39; -15,49</t>
+          <t>-28,94; -15,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -9,66</t>
+          <t>-23,27; -10,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 6,31</t>
+          <t>-7,51; 6,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,88; -10,0</t>
+          <t>-21,86; -10,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 35,28</t>
+          <t>-19,25; -7,47</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,95</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>-4,97</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>-3,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,61; -1,03</t>
+          <t>-11,8; -0,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,86; -1,35</t>
+          <t>-12,16; -1,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 3,62</t>
+          <t>-6,7; 4,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 1,01</t>
+          <t>-9,75; 1,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,98; -2,74</t>
+          <t>-13,71; -2,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 24,08</t>
+          <t>-9,75; -0,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,25; -1,36</t>
+          <t>-9,03; -1,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -3,19</t>
+          <t>-10,89; -3,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 19,08</t>
+          <t>-6,88; 0,68</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-4,17%</t>
+          <t>-3,05%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>-8,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>-6,18%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,59; -2,51</t>
+          <t>-23,38; -0,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,84; -2,64</t>
+          <t>-24,65; -2,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 8,19</t>
+          <t>-13,73; 10,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 1,73</t>
+          <t>-16,6; 1,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,92; -4,98</t>
+          <t>-23,08; -5,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 42,5</t>
+          <t>-16,37; -0,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,09; -2,66</t>
+          <t>-16,75; -2,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,48; -6,4</t>
+          <t>-20,22; -6,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 37,11</t>
+          <t>-12,91; 1,38</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,21</t>
+          <t>8,7</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>5,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 7,97</t>
+          <t>-1,61; 7,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -1,49</t>
+          <t>-9,96; -1,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 14,95</t>
+          <t>4,15; 13,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 5,6</t>
+          <t>-3,08; 5,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,67; -4,03</t>
+          <t>-12,9; -3,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 4,7</t>
+          <t>-1,98; 6,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 5,22</t>
+          <t>-0,95; 5,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,05; -4,05</t>
+          <t>-10,18; -4,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 7,87</t>
+          <t>2,09; 8,41</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,27%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 19,69</t>
+          <t>-3,68; 18,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,19; -3,52</t>
+          <t>-22,15; -2,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,0; 37,26</t>
+          <t>8,69; 32,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 10,88</t>
+          <t>-5,5; 11,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,69; -7,77</t>
+          <t>-22,9; -7,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 8,84</t>
+          <t>-3,51; 11,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 11,14</t>
+          <t>-1,91; 11,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,23; -8,62</t>
+          <t>-20,21; -8,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 16,73</t>
+          <t>4,11; 17,83</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-4,12</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>-0,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,93</t>
+          <t>-1,03; 3,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,05; -1,24</t>
+          <t>-5,88; -1,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 17,79</t>
+          <t>0,49; 5,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,05; -0,07</t>
+          <t>-5,27; -0,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,47; -6,64</t>
+          <t>-11,41; -6,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 5,95</t>
+          <t>-6,22; -1,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,96</t>
+          <t>-2,44; 1,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -4,78</t>
+          <t>-8,19; -4,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 9,1</t>
+          <t>-2,34; 1,15</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,09%</t>
+          <t>-7,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>-1,23%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 9,51</t>
+          <t>-2,37; 9,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -2,98</t>
+          <t>-13,47; -2,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,88; 41,8</t>
+          <t>1,13; 13,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,72; -0,14</t>
+          <t>-8,99; -0,74</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,76; -11,82</t>
+          <t>-19,85; -12,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 10,58</t>
+          <t>-10,65; -3,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 1,93</t>
+          <t>-4,77; 2,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,08; -9,73</t>
+          <t>-16,04; -9,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 18,35</t>
+          <t>-4,61; 2,38</t>
         </is>
       </c>
     </row>
